--- a/6_patentreports/1_antibiotic_resistance/3_additional_analyses_and_report_output/temporal_pair_evolution.xlsx
+++ b/6_patentreports/1_antibiotic_resistance/3_additional_analyses_and_report_output/temporal_pair_evolution.xlsx
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2535</v>
+        <v>2880</v>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E2" t="n">
-        <v>776</v>
+        <v>841</v>
       </c>
       <c r="F2" t="n">
-        <v>645</v>
+        <v>702</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2240</v>
+        <v>2837</v>
       </c>
       <c r="C3" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D3" t="n">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="E3" t="n">
-        <v>632</v>
+        <v>805</v>
       </c>
       <c r="F3" t="n">
-        <v>459</v>
+        <v>603</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4388</v>
+        <v>4524</v>
       </c>
       <c r="C4" t="n">
         <v>195</v>
@@ -535,10 +535,10 @@
         <v>291</v>
       </c>
       <c r="E4" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F4" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -549,23 +549,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Medical Technology</t>
+          <t>Food Preservation &lt;-&gt; Medical Technology</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2673</v>
+        <v>830</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E5" t="n">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="F5" t="n">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -576,23 +576,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Drug Delivery &lt;-&gt; Medical Technology</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Medical Technology</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>3050</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="E6" t="n">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="F6" t="n">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -603,23 +603,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Drug Formulations &lt;-&gt; Medical Technology</t>
+          <t>Drug Delivery &lt;-&gt; Medical Technology</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>991</v>
+        <v>879</v>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="F7" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -630,23 +630,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antiinfective Therapy &lt;-&gt; Drug Formulations</t>
+          <t>Drug Formulations &lt;-&gt; Medical Technology</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>947</v>
+        <v>1103</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Combinations</t>
+          <t>Antiinfective Therapy &lt;-&gt; Drug Formulations</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1718</v>
+        <v>1003</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -684,23 +684,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biochemistry &lt;-&gt; Microbial Testing</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Combinations</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>978</v>
+        <v>1746</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -711,23 +711,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Antibiotic Drugs (Peptides)</t>
+          <t>Biochemistry &lt;-&gt; Microbial Testing</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>987</v>
+        <v>1106</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -738,23 +738,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Formulations</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Antibiotic Drugs (Peptides)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1394</v>
+        <v>1006</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -765,23 +765,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Drug Delivery &lt;-&gt; Drug Formulations</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Formulations</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>896</v>
+        <v>1494</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -792,23 +792,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Genetic Engineering &lt;-&gt; Microbial Testing</t>
+          <t>Drug Delivery &lt;-&gt; Drug Formulations</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>871</v>
+        <v>992</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Chemistry (Heterocyclic)</t>
+          <t>Genetic Engineering &lt;-&gt; Microbial Testing</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3233</v>
+        <v>912</v>
       </c>
       <c r="C15" t="n">
         <v>83</v>
       </c>
       <c r="D15" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -846,23 +846,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Delivery</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Chemistry (Heterocyclic)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1155</v>
+        <v>3257</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -873,23 +873,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agriculture &amp; Biocides &lt;-&gt; Antibiotic Drugs (Organic)</t>
+          <t>Antibiotic Drugs (Organic) &lt;-&gt; Drug Delivery</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>753</v>
+        <v>1256</v>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="C18" t="n">
         <v>80</v>
@@ -913,10 +913,10 @@
         <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>790</v>
+        <v>821</v>
       </c>
       <c r="C19" t="n">
         <v>57</v>
@@ -940,10 +940,10 @@
         <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="C20" t="n">
         <v>56</v>
